--- a/indicadores/SFE-EIPP_out.xlsx
+++ b/indicadores/SFE-EIPP_out.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">25/09/2026</t>
+    <t xml:space="preserve">28/09/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>

--- a/indicadores/SFE-EIPP_out.xlsx
+++ b/indicadores/SFE-EIPP_out.xlsx
@@ -116,7 +116,7 @@
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">arodriguez</t>
+    <t xml:space="preserve">pcohan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
